--- a/_101_Items.xlsx
+++ b/_101_Items.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\UnityPortfolioProjectTables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1593553F-3236-477D-9A1B-6DAA8D8FF6A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D01B83BC-1BEB-4F61-A6D6-A16C1950DC54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" xr2:uid="{8996C81C-FF45-4FA2-B6CE-365CE91B1C33}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="12">
   <si>
     <t>key</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -50,10 +50,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>start</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Gold</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -63,6 +59,30 @@
   </si>
   <si>
     <t>PlayerExp</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>name</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>icon</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>x</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>EItemType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>type</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9000001</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -501,7 +521,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BB77E38-BF09-42DC-A18A-223E5D5C39AB}">
-  <dimension ref="A2:C54"/>
+  <dimension ref="A2:D54"/>
   <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="12.5703125" style="7" customWidth="1"/>
@@ -511,97 +531,122 @@
     <col min="11" max="37" width="12.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" s="8"/>
-    </row>
-    <row r="3" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+        <v>10</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="4" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="8"/>
-    </row>
-    <row r="4" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="4" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="5">
         <v>1010001</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" s="9"/>
-    </row>
-    <row r="5" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+        <v>5</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="6">
         <v>1010002</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C5" s="10"/>
-    </row>
-    <row r="6" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+        <v>3</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="5">
         <v>1010003</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="C6" s="9"/>
-    </row>
-    <row r="7" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+        <v>4</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="6"/>
       <c r="B7" s="10"/>
       <c r="C7" s="10"/>
     </row>
-    <row r="8" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="5"/>
       <c r="B8" s="9"/>
       <c r="C8" s="9"/>
     </row>
-    <row r="9" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="6"/>
       <c r="B9" s="10"/>
       <c r="C9" s="10"/>
     </row>
-    <row r="10" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="5"/>
       <c r="B10" s="9"/>
       <c r="C10" s="9"/>
     </row>
-    <row r="11" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="6"/>
       <c r="B11" s="10"/>
       <c r="C11" s="10"/>
     </row>
-    <row r="12" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="5"/>
       <c r="B12" s="9"/>
       <c r="C12" s="9"/>
     </row>
-    <row r="13" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="6"/>
       <c r="B13" s="10"/>
       <c r="C13" s="10"/>
     </row>
-    <row r="14" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="5"/>
       <c r="B14" s="9"/>
       <c r="C14" s="9"/>
     </row>
-    <row r="15" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="6"/>
       <c r="B15" s="10"/>
       <c r="C15" s="10"/>
     </row>
-    <row r="16" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="5"/>
       <c r="B16" s="9"/>
       <c r="C16" s="9"/>
